--- a/ventas/seguimiento_clientes.xlsx
+++ b/ventas/seguimiento_clientes.xlsx
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">1b. Ya venden por WhatsApp</t>
   </si>
   <si>
-    <t xml:space="preserve">Buenas, ¿hablo con {nombre}? Mi nombre es {su nombre}. Vi que reciben los pedidos por WhatsApp. A la hora del almuerzo, ¿quién contesta todos esos mensajes? Tenemos un asistente que los contesta solo: toma el pedido, confirma la dirección, calcula el domicilio, revisa el comprobante de la transferencia y le manda la comanda a la cocina. Usted solo revisa. ¿Le muestro cómo quedaría con su menú?</t>
+    <t xml:space="preserve">Buenas, ¿hablo con {nombre}? Mi nombre es {su nombre}. Vi que reciben los pedidos por WhatsApp. A la hora del almuerzo, ¿quién contesta todos esos mensajes? Tenemos un asistente que los contesta solo: toma el pedido, confirma la dirección, calcula el domicilio, revisa el comprobante de la transferencia y le manda la comanda a la cocina. Sigue con su mismo número y su app de WhatsApp, y usted ve todos los chats. ¿Le muestro cómo quedaría con su menú?</t>
   </si>
   <si>
     <t xml:space="preserve">2. Si hacen domicilios</t>
